--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
+++ b/branches/Richard/StructureDefinition-patient-pegnancy-staus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
